--- a/docs/regagg/execution/Execution_Status.xlsx
+++ b/docs/regagg/execution/Execution_Status.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Summary" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Story Status'!$A$1:$K$73</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Story Status'!$A$1:$K$103</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Test Cases'!$A$1:$H$107</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1596" uniqueCount="737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1888" uniqueCount="885">
   <si>
     <t xml:space="preserve">Story ID</t>
   </si>
@@ -1052,6 +1052,450 @@
   </si>
   <si>
     <t xml:space="preserve">Pending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REG-801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Migration &amp; Data Platform (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure-as-code baseline for the aggregator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Codify the aggregator's AWS footprint (RDS access, S3 buckets/prefixes, ECR repo, ECS task definitions, EventBridge rules, IAM roles) as reviewable IaC in the platform's existing tooling, with per-environment parameters.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dev/staging/prod stacks deploy from code with no console steps; IAM follows least privilege; teardown/redeploy reproduces an identical environment; peer-reviewed and merged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requires platform/DevOps skills — see capacity assumption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REG-802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PostgreSQL migration &amp; schema deployment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deploy the reg_* schema into the existing production PostgreSQL (namespaced, no collisions with platform tables) and migrate the SQLite corpus index with full fidelity; establish forward migration tooling.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All 9 reg_* tables created via versioned migration; row counts and invariants match source exactly; one-current-per-doc enforced by partial unique index; rollback path documented; full test suite green against Postgres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDL shipped (003_regagg_schema.sql); reg_ prefix already prevents collisions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REG-803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3 storage cutover for corpus and markdown projection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Switch the storage backend from local disk to S3 for the canonical corpus (raw/meta/versions/archive) and the agent-facing markdown projection, preserving the exact key layout the agent tools consume.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Existing ~6GB corpus migrated with checksum verification; ingestion writes to S3; projection paths unchanged for agent tools; archive immutability enforced via bucket policy/versioning; no local-disk dependency remains</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Storage abstraction already supports s3 backend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REG-804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secrets and environment configuration management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Move API keys, database credentials and per-environment settings into the platform's secrets manager/parameter store; remove file-based keys; document rotation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No credential exists in the repo or on disk; application resolves secrets at runtime per environment; key rotation performed without redeploy; rotation SOP documented</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Local build already rotated keys to DB-only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REG-805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Containerise collection workers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Package the collection pipeline as a container image (pinned dependencies, non-root, health check) published to the registry, runnable as a one-shot task.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Image builds reproducibly in CI; a task run performs a full regulator ingest against RDS+S3; image scanned for vulnerabilities with no criticals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REG-806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud-scheduled daily and weekly ingestion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Replace host cron with cloud scheduling: daily delta run and weekly deep run as scheduled container tasks, with concurrency guard, timeout, retry and failure notification.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily/weekly schedules fire reliably; overlapping runs prevented; failures raise an alert; run history visible in the existing dashboard exactly as today</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poller entrypoint + single-run guard already built</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REG-807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud backup, retention and restore drill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adopt platform-native durability: RDS automated backups with point-in-time recovery, S3 versioning plus lifecycle tiering for archive, and a documented restore procedure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PITR verified by restoring to a scratch instance; S3 versioning protects against accidental deletion; lifecycle policy moves cold archive to cheaper tier; restore drill timed and documented against RPO/RTO targets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Local backup script is the interim control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REG-808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BA: data classification, residency and retention sign-off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirm classification of the corpus (public regulatory content plus internal metadata), residency requirements and retention obligations for the cloud footprint.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Classification recorded; residency constraints reflected in region/bucket choices; retention schedule agreed with compliance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PM-S7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PM: sprint ceremonies, cloud dependency management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recurring PM allocation plus coordination with the platform team.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ceremonies held; cross-team dependencies tracked; sprint report issued</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REG-901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Integration, Security &amp; Operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Register reg_* tools on the production MCP server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deploy the twelve reg_* tool definitions into the existing production MCP server so the production agent can call them, without forking platform code.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All twelve tools discoverable and callable in production; naming does not collide with existing platform tools; mutating tool (trigger run) gated by role; smoke test from the production agent passes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tools are config-driven; index+content planes already built</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REG-902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scale &amp; Performance (100 → 5,000 users)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eliminate per-row object-store reads on the read path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove N+1 storage reads: persist document excerpts as a database column at ingest instead of reading each markdown file per listing row, and stop reading document bodies during search scoring.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corpus listing issues a single database query with zero object-store calls; excerpt backfilled for existing corpus and maintained at ingest; p95 listing latency under target with cold cache</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Measured defect: 50-row page = 50 object reads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REG-903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delegate content search to the platform search layer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Point content retrieval at the platform's existing BM25/RAG index over the markdown projection, keeping the filter-then-rank contract; retire the interim in-process scorer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reg_search filters in SQL then ranks via the platform index; results and citations equivalent or better than interim ranker; latency budget met on the full corpus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner's stack already provides BM25/RAG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REG-904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horizontally scalable stateless read tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run the dashboard/API tier as stateless replicas behind the platform load balancer with autoscaling, connection pooling to RDS, and graceful shutdown.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service scales out and in under load with no session affinity; database connections bounded and pooled; rolling deploy causes no failed requests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thread-scoped sessions already fix pool leakage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REG-905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Response caching for hot read endpoints</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cache coverage tree, facet counts and change-feed responses with short, explicit TTLs and invalidation on ingest completion.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repeat dashboard loads served from cache; cache invalidated within one minute of a completed run; cache hit ratio and staleness observable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REG-906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSO authentication and role-based access control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Replace single-operator access with platform SSO and two roles: analyst (read) and operator (run, toggle, manual ingest); identity flows into the existing audit trail.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unauthenticated access refused; analysts cannot trigger runs or manual ingests; every mutating action recorded with the authenticated identity; access matrix matches the signed-off definition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Audit trail and operator attribution already implemented</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REG-907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per-tenant API keys, quotas and rate limiting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Issue scoped keys per team/agent with request quotas and rate limits so one consumer cannot degrade the service for 5,000 users.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keys scoped to reg_* tools; quota and rate limit enforced with clear error responses; usage attributable per key; limits configurable without redeploy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allowlist enforcement already built</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REG-908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Queue-based parallel ingestion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Introduce a work queue between detection and fetch so multiple workers process documents concurrently, keeping the daily window comfortable as coverage depth grows, while preserving per-regulator politeness limits.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full fleet run completes within the agreed window; per-domain rate limits still honoured; failures isolated per document; ordering-independent and idempotent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pipeline is already stateless and idempotent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REG-909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BA: role and access matrix definition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Define analyst/operator/administrator permissions across UI and tools and obtain security sign-off.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matrix signed off; mapped to implemented roles; exceptions documented</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PM-S8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PM: sprint ceremonies, integration coordination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recurring PM allocation plus platform-team integration coordination.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ceremonies held; integration risks tracked; sprint report issued</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REG-1001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load and soak testing to 5,000 users</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Define SLOs and prove them: model realistic analyst and agent traffic, run peak-load and multi-hour soak tests including a concurrent ingestion window.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agreed SLOs documented; peak load sustained within latency budgets; soak shows no memory/connection leak; results reported with headroom analysis and breaking point identified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read load is user-driven; collection load is fixed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REG-1002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Performance tuning from load-test findings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Address the bottlenecks the load test surfaces: query plans and indexes, pagination limits, payload sizes, and any remaining chatty calls.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each identified bottleneck has a measured before/after; SLOs met with agreed headroom; changes covered by regression tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REG-1003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability: metrics, logs and dashboards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emit structured logs and service metrics (ingestion volume and errors, corpus freshness, tool latency and error rate, queue depth) into the platform's monitoring stack with an operations dashboard.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Golden signals visible per service; ingestion and corpus health tracked over time; logs correlatable by run and request identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run manifests and counters already provide the data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REG-1004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alerting and operational runbooks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alert on the conditions that matter — failed or missed daily run, regulator staleness beyond threshold, integrity violation, elevated tool error rate — each with a runbook.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every alert has an owner, severity and runbook; alerts tested by injecting each condition; no alert without a documented response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integrity check already exits non-zero on violations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REG-1005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD pipeline with automated quality gates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate build, test and deployment: full test suite and foundation gate on every change, image build and scan, staged deployment with rollback.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No manual deployment steps; pipeline blocks on failing tests or critical vulnerabilities; rollback exercised successfully at least once</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92-test suite + foundation gate ready to wire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REG-1006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security review and hardening</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complete pre-production security work: TLS everywhere, no default credentials, least-privilege IAM and bucket policies, dependency and image scanning, remediation of review findings.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security review passed with no open high findings; default credentials eliminated; egress allow-list covers regulator domains; findings tracked to closure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANDATORY gate before exposure beyond localhost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REG-1007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost model and optimisation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model steady-state cost (compute, RDS, S3 storage and requests, egress) at 5,000 users and apply the obvious optimisations; set budget alarms.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost per month projected with assumptions stated; S3 lifecycle tiering applied to archive; budget alarm configured; unit cost per user reported</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REG-1008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production cutover and hypercare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Execute the cutover: final data sync, DNS/route switch, agent repointed to production tools, decommission of the interim environment, and a defined hypercare period.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cutover run to a rehearsed plan with rollback available; no data loss verified by count and checksum; hypercare issues triaged daily; interim environment retired</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REG-1009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BA: production acceptance and go-live sign-off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run acceptance against production with real users and obtain formal go-live approval.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acceptance script executed in production; defects dispositioned; signed go-live approval recorded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PM-S9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PM: sprint ceremonies, security &amp; integration coordination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Readiness review, cutover coordination, hypercare tracking and project closure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Go/no-go held with documented decision; cutover coordinated; closure report issued</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PM-S10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PM: hypercare tracking and project closure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final sprint PM allocation: cutover coordination, hypercare triage, closure report and handover.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hypercare issues triaged daily; closure report issued; handover acknowledged</t>
   </si>
   <si>
     <t xml:space="preserve">REG-701</t>
@@ -2656,7 +3100,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K73"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -4876,132 +5320,132 @@
         <v>341</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
         <v>342</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>303</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>303</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>5</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>303</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>3</v>
@@ -5013,66 +5457,66 @@
         <v>303</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>303</v>
       </c>
       <c r="K68" s="2"/>
     </row>
-    <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>343</v>
+        <v>370</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>18</v>
@@ -5081,138 +5525,136 @@
         <v>303</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>343</v>
+        <v>370</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>303</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="K71" s="2" t="s">
-        <v>381</v>
-      </c>
+      <c r="K71" s="2"/>
     </row>
     <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>303</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>386</v>
+        <v>71</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>326</v>
+        <v>389</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>327</v>
+        <v>390</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>343</v>
+        <v>391</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>53</v>
@@ -5221,11 +5663,1047 @@
         <v>303</v>
       </c>
       <c r="K73" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="K75" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="K77" s="2"/>
+    </row>
+    <row r="78" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="D78" s="2" t="s">
         <v>391</v>
       </c>
+      <c r="E78" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="K81" s="2"/>
+    </row>
+    <row r="82" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="K82" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="K83" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="K84" s="2"/>
+    </row>
+    <row r="85" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J85" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="K85" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J87" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="K87" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="K88" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J89" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="K89" s="2"/>
+    </row>
+    <row r="90" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J90" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="K90" s="2"/>
+    </row>
+    <row r="91" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J91" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="K91" s="2"/>
+    </row>
+    <row r="92" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J92" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="K92" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J93" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="K93" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J94" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="K94" s="2" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J95" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="K95" s="2" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J96" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="K96" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J97" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="K97" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J98" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="K98" s="2"/>
+    </row>
+    <row r="99" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J99" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="K99" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J100" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="K100" s="2" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I101" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J101" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="K101" s="2" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J102" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="K102" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J103" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="K103" s="2" t="s">
+        <v>539</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K73"/>
+  <autoFilter ref="A1:K103"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -5257,7 +6735,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>392</v>
+        <v>540</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -5266,388 +6744,388 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>393</v>
+        <v>541</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>394</v>
+        <v>542</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>395</v>
+        <v>543</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>396</v>
+        <v>544</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>397</v>
+        <v>545</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>398</v>
+        <v>546</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>170</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>399</v>
+        <v>547</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>400</v>
+        <v>548</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>401</v>
+        <v>549</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>403</v>
+        <v>551</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>404</v>
+        <v>552</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>398</v>
+        <v>546</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>170</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>399</v>
+        <v>547</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>405</v>
+        <v>553</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>401</v>
+        <v>549</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>406</v>
+        <v>554</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>407</v>
+        <v>555</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>398</v>
+        <v>546</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>170</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>399</v>
+        <v>547</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>408</v>
+        <v>556</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>401</v>
+        <v>549</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>409</v>
+        <v>557</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>410</v>
+        <v>558</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>398</v>
+        <v>546</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>170</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>399</v>
+        <v>547</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>411</v>
+        <v>559</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>401</v>
+        <v>549</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>412</v>
+        <v>560</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>413</v>
+        <v>561</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>398</v>
+        <v>546</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>170</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>399</v>
+        <v>547</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>414</v>
+        <v>562</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>401</v>
+        <v>549</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>415</v>
+        <v>563</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>416</v>
+        <v>564</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>417</v>
+        <v>565</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>91</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>399</v>
+        <v>547</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>418</v>
+        <v>566</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>419</v>
+        <v>567</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>420</v>
+        <v>568</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>421</v>
+        <v>569</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>417</v>
+        <v>565</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>91</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>399</v>
+        <v>547</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>422</v>
+        <v>570</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>419</v>
+        <v>567</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>423</v>
+        <v>571</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>424</v>
+        <v>572</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>417</v>
+        <v>565</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>91</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>399</v>
+        <v>547</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>425</v>
+        <v>573</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>419</v>
+        <v>567</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>426</v>
+        <v>574</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>427</v>
+        <v>575</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>417</v>
+        <v>565</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>91</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>399</v>
+        <v>547</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>428</v>
+        <v>576</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>419</v>
+        <v>567</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>429</v>
+        <v>577</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>430</v>
+        <v>578</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>417</v>
+        <v>565</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>91</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>399</v>
+        <v>547</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>431</v>
+        <v>579</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>419</v>
+        <v>567</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>432</v>
+        <v>580</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>433</v>
+        <v>581</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>417</v>
+        <v>565</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>91</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>399</v>
+        <v>547</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>434</v>
+        <v>582</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>419</v>
+        <v>567</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>435</v>
+        <v>583</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>436</v>
+        <v>584</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>387</v>
+        <v>535</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>199</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>437</v>
+        <v>585</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>438</v>
+        <v>586</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>439</v>
+        <v>587</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>440</v>
+        <v>588</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>441</v>
+        <v>589</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>387</v>
+        <v>535</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>199</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>437</v>
+        <v>585</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>442</v>
+        <v>590</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>439</v>
+        <v>587</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>443</v>
+        <v>591</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>444</v>
+        <v>592</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>387</v>
+        <v>535</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>199</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>437</v>
+        <v>585</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>445</v>
+        <v>593</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>439</v>
+        <v>587</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>446</v>
+        <v>594</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>447</v>
+        <v>595</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>107</v>
@@ -5656,24 +7134,24 @@
         <v>91</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>448</v>
+        <v>596</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>449</v>
+        <v>597</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>450</v>
+        <v>598</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>451</v>
+        <v>599</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>452</v>
+        <v>600</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>107</v>
@@ -5682,24 +7160,24 @@
         <v>91</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>448</v>
+        <v>596</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>453</v>
+        <v>601</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>450</v>
+        <v>598</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>454</v>
+        <v>602</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>455</v>
+        <v>603</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>107</v>
@@ -5708,24 +7186,24 @@
         <v>91</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>448</v>
+        <v>596</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>456</v>
+        <v>604</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>450</v>
+        <v>598</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>457</v>
+        <v>605</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>458</v>
+        <v>606</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>107</v>
@@ -5734,232 +7212,232 @@
         <v>91</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>448</v>
+        <v>596</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>459</v>
+        <v>607</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>450</v>
+        <v>598</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>460</v>
+        <v>608</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>461</v>
+        <v>609</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>462</v>
+        <v>610</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>259</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>399</v>
+        <v>547</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>463</v>
+        <v>611</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>464</v>
+        <v>612</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>465</v>
+        <v>613</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>466</v>
+        <v>614</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>462</v>
+        <v>610</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>259</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>399</v>
+        <v>547</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>467</v>
+        <v>615</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>464</v>
+        <v>612</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>468</v>
+        <v>616</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>469</v>
+        <v>617</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>462</v>
+        <v>610</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>259</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>399</v>
+        <v>547</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>470</v>
+        <v>618</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>464</v>
+        <v>612</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>471</v>
+        <v>619</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>472</v>
+        <v>620</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>462</v>
+        <v>610</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>259</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>399</v>
+        <v>547</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>473</v>
+        <v>621</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>464</v>
+        <v>612</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>474</v>
+        <v>622</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>475</v>
+        <v>623</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>462</v>
+        <v>610</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>259</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>399</v>
+        <v>547</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>476</v>
+        <v>624</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>464</v>
+        <v>612</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>477</v>
+        <v>625</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>478</v>
+        <v>626</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>462</v>
+        <v>610</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>259</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>399</v>
+        <v>547</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>479</v>
+        <v>627</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>464</v>
+        <v>612</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>480</v>
+        <v>628</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>481</v>
+        <v>629</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>462</v>
+        <v>610</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>259</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>399</v>
+        <v>547</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>482</v>
+        <v>630</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>464</v>
+        <v>612</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>483</v>
+        <v>631</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>484</v>
+        <v>632</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>462</v>
+        <v>610</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>259</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>399</v>
+        <v>547</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>485</v>
+        <v>633</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>464</v>
+        <v>612</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>486</v>
+        <v>634</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>487</v>
+        <v>635</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>139</v>
@@ -5968,24 +7446,24 @@
         <v>118</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>399</v>
+        <v>547</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>488</v>
+        <v>636</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>489</v>
+        <v>637</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>490</v>
+        <v>638</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>491</v>
+        <v>639</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>139</v>
@@ -5994,24 +7472,24 @@
         <v>118</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>399</v>
+        <v>547</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>492</v>
+        <v>640</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>489</v>
+        <v>637</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>493</v>
+        <v>641</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>494</v>
+        <v>642</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>55</v>
@@ -6020,24 +7498,24 @@
         <v>48</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>495</v>
+        <v>643</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>496</v>
+        <v>644</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>497</v>
+        <v>645</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>498</v>
+        <v>646</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>499</v>
+        <v>647</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>55</v>
@@ -6046,24 +7524,24 @@
         <v>48</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>495</v>
+        <v>643</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>496</v>
+        <v>644</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>497</v>
+        <v>645</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>500</v>
+        <v>648</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>501</v>
+        <v>649</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>55</v>
@@ -6072,24 +7550,24 @@
         <v>48</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>495</v>
+        <v>643</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>496</v>
+        <v>644</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>497</v>
+        <v>645</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>502</v>
+        <v>650</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>503</v>
+        <v>651</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>55</v>
@@ -6098,24 +7576,24 @@
         <v>48</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>495</v>
+        <v>643</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>496</v>
+        <v>644</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>497</v>
+        <v>645</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>504</v>
+        <v>652</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>505</v>
+        <v>653</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>55</v>
@@ -6124,24 +7602,24 @@
         <v>48</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>495</v>
+        <v>643</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>496</v>
+        <v>644</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>497</v>
+        <v>645</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>506</v>
+        <v>654</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>507</v>
+        <v>655</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>55</v>
@@ -6150,24 +7628,24 @@
         <v>48</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>495</v>
+        <v>643</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>496</v>
+        <v>644</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>497</v>
+        <v>645</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>508</v>
+        <v>656</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>509</v>
+        <v>657</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>55</v>
@@ -6176,24 +7654,24 @@
         <v>48</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>495</v>
+        <v>643</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>496</v>
+        <v>644</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>497</v>
+        <v>645</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>510</v>
+        <v>658</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>511</v>
+        <v>659</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>55</v>
@@ -6202,24 +7680,24 @@
         <v>48</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>495</v>
+        <v>643</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>496</v>
+        <v>644</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>497</v>
+        <v>645</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>512</v>
+        <v>660</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>513</v>
+        <v>661</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>55</v>
@@ -6228,24 +7706,24 @@
         <v>48</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>495</v>
+        <v>643</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>496</v>
+        <v>644</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>497</v>
+        <v>645</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>514</v>
+        <v>662</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>515</v>
+        <v>663</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>55</v>
@@ -6254,24 +7732,24 @@
         <v>48</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>495</v>
+        <v>643</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>496</v>
+        <v>644</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>497</v>
+        <v>645</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>516</v>
+        <v>664</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>517</v>
+        <v>665</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>55</v>
@@ -6280,24 +7758,24 @@
         <v>48</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>495</v>
+        <v>643</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>496</v>
+        <v>644</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>497</v>
+        <v>645</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>518</v>
+        <v>666</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>519</v>
+        <v>667</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>55</v>
@@ -6306,24 +7784,24 @@
         <v>48</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>495</v>
+        <v>643</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>496</v>
+        <v>644</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>497</v>
+        <v>645</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>520</v>
+        <v>668</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>521</v>
+        <v>669</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>55</v>
@@ -6332,24 +7810,24 @@
         <v>48</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>495</v>
+        <v>643</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>496</v>
+        <v>644</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>497</v>
+        <v>645</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>522</v>
+        <v>670</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>523</v>
+        <v>671</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>55</v>
@@ -6358,24 +7836,24 @@
         <v>48</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>495</v>
+        <v>643</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>496</v>
+        <v>644</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>497</v>
+        <v>645</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>524</v>
+        <v>672</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>525</v>
+        <v>673</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>55</v>
@@ -6384,24 +7862,24 @@
         <v>48</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>495</v>
+        <v>643</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>496</v>
+        <v>644</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>497</v>
+        <v>645</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>526</v>
+        <v>674</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>527</v>
+        <v>675</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>55</v>
@@ -6410,24 +7888,24 @@
         <v>48</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>495</v>
+        <v>643</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>496</v>
+        <v>644</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>497</v>
+        <v>645</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>528</v>
+        <v>676</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>529</v>
+        <v>677</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>55</v>
@@ -6436,24 +7914,24 @@
         <v>48</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>495</v>
+        <v>643</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>496</v>
+        <v>644</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>497</v>
+        <v>645</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>530</v>
+        <v>678</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>531</v>
+        <v>679</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>55</v>
@@ -6462,24 +7940,24 @@
         <v>48</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>495</v>
+        <v>643</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>496</v>
+        <v>644</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>497</v>
+        <v>645</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>532</v>
+        <v>680</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>533</v>
+        <v>681</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>55</v>
@@ -6488,24 +7966,24 @@
         <v>48</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>495</v>
+        <v>643</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>496</v>
+        <v>644</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>497</v>
+        <v>645</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>534</v>
+        <v>682</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>535</v>
+        <v>683</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>55</v>
@@ -6514,24 +7992,24 @@
         <v>48</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>495</v>
+        <v>643</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>496</v>
+        <v>644</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>497</v>
+        <v>645</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>536</v>
+        <v>684</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>537</v>
+        <v>685</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>55</v>
@@ -6540,24 +8018,24 @@
         <v>48</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>495</v>
+        <v>643</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>496</v>
+        <v>644</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>497</v>
+        <v>645</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>538</v>
+        <v>686</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>539</v>
+        <v>687</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>55</v>
@@ -6566,24 +8044,24 @@
         <v>48</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>495</v>
+        <v>643</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>496</v>
+        <v>644</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>497</v>
+        <v>645</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>540</v>
+        <v>688</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>541</v>
+        <v>689</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>55</v>
@@ -6592,24 +8070,24 @@
         <v>48</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>495</v>
+        <v>643</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>496</v>
+        <v>644</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>497</v>
+        <v>645</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>542</v>
+        <v>690</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>543</v>
+        <v>691</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>55</v>
@@ -6618,24 +8096,24 @@
         <v>48</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>495</v>
+        <v>643</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>496</v>
+        <v>644</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>497</v>
+        <v>645</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>544</v>
+        <v>692</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>545</v>
+        <v>693</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>55</v>
@@ -6644,24 +8122,24 @@
         <v>48</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>495</v>
+        <v>643</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>496</v>
+        <v>644</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>497</v>
+        <v>645</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>546</v>
+        <v>694</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>547</v>
+        <v>695</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>55</v>
@@ -6670,24 +8148,24 @@
         <v>48</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>495</v>
+        <v>643</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>496</v>
+        <v>644</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>497</v>
+        <v>645</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>548</v>
+        <v>696</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>549</v>
+        <v>697</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>55</v>
@@ -6696,24 +8174,24 @@
         <v>48</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>495</v>
+        <v>643</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>496</v>
+        <v>644</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>497</v>
+        <v>645</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>550</v>
+        <v>698</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>551</v>
+        <v>699</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>55</v>
@@ -6722,24 +8200,24 @@
         <v>48</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>495</v>
+        <v>643</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>496</v>
+        <v>644</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>497</v>
+        <v>645</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>552</v>
+        <v>700</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>553</v>
+        <v>701</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>55</v>
@@ -6748,24 +8226,24 @@
         <v>48</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>495</v>
+        <v>643</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>496</v>
+        <v>644</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>497</v>
+        <v>645</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>554</v>
+        <v>702</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>555</v>
+        <v>703</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>55</v>
@@ -6774,492 +8252,492 @@
         <v>48</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>495</v>
+        <v>643</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>556</v>
+        <v>704</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>497</v>
+        <v>645</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>557</v>
+        <v>705</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
-        <v>558</v>
+        <v>706</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>559</v>
+        <v>707</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>199</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>560</v>
+        <v>708</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>561</v>
+        <v>709</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>562</v>
+        <v>710</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>563</v>
+        <v>711</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
-        <v>564</v>
+        <v>712</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>559</v>
+        <v>707</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>199</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>560</v>
+        <v>708</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>565</v>
+        <v>713</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>562</v>
+        <v>710</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>566</v>
+        <v>714</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>567</v>
+        <v>715</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>559</v>
+        <v>707</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>199</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>560</v>
+        <v>708</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>568</v>
+        <v>716</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>562</v>
+        <v>710</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>569</v>
+        <v>717</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
-        <v>570</v>
+        <v>718</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>559</v>
+        <v>707</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>199</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>560</v>
+        <v>708</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>571</v>
+        <v>719</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>562</v>
+        <v>710</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>572</v>
+        <v>720</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
-        <v>573</v>
+        <v>721</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>559</v>
+        <v>707</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>199</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>560</v>
+        <v>708</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>574</v>
+        <v>722</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>562</v>
+        <v>710</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>575</v>
+        <v>723</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
-        <v>576</v>
+        <v>724</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>559</v>
+        <v>707</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>199</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>560</v>
+        <v>708</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>577</v>
+        <v>725</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>562</v>
+        <v>710</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>578</v>
+        <v>726</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
-        <v>579</v>
+        <v>727</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>559</v>
+        <v>707</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>199</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>560</v>
+        <v>708</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>580</v>
+        <v>728</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>562</v>
+        <v>710</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>581</v>
+        <v>729</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2" t="s">
-        <v>582</v>
+        <v>730</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>583</v>
+        <v>731</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>170</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>584</v>
+        <v>732</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>585</v>
+        <v>733</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>586</v>
+        <v>734</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>587</v>
+        <v>735</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
-        <v>588</v>
+        <v>736</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>583</v>
+        <v>731</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>170</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>584</v>
+        <v>732</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>589</v>
+        <v>737</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>586</v>
+        <v>734</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>590</v>
+        <v>738</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="s">
-        <v>591</v>
+        <v>739</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>583</v>
+        <v>731</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>170</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>584</v>
+        <v>732</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>592</v>
+        <v>740</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>586</v>
+        <v>734</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>593</v>
+        <v>741</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
-        <v>594</v>
+        <v>742</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>583</v>
+        <v>731</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>170</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>584</v>
+        <v>732</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>595</v>
+        <v>743</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>586</v>
+        <v>734</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>596</v>
+        <v>744</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
-        <v>597</v>
+        <v>745</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>583</v>
+        <v>731</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>170</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>584</v>
+        <v>732</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>598</v>
+        <v>746</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>586</v>
+        <v>734</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>599</v>
+        <v>747</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="s">
-        <v>600</v>
+        <v>748</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>583</v>
+        <v>731</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>170</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>584</v>
+        <v>732</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>601</v>
+        <v>749</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>586</v>
+        <v>734</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>602</v>
+        <v>750</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
-        <v>603</v>
+        <v>751</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>583</v>
+        <v>731</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>170</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>584</v>
+        <v>732</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>604</v>
+        <v>752</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>586</v>
+        <v>734</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>605</v>
+        <v>753</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
-        <v>606</v>
+        <v>754</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>583</v>
+        <v>731</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>170</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>584</v>
+        <v>732</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>607</v>
+        <v>755</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>586</v>
+        <v>734</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>608</v>
+        <v>756</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
-        <v>609</v>
+        <v>757</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>583</v>
+        <v>731</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>170</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>584</v>
+        <v>732</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>610</v>
+        <v>758</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>586</v>
+        <v>734</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>611</v>
+        <v>759</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
-        <v>612</v>
+        <v>760</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>583</v>
+        <v>731</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>170</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>584</v>
+        <v>732</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>613</v>
+        <v>761</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>586</v>
+        <v>734</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>614</v>
+        <v>762</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2" t="s">
-        <v>615</v>
+        <v>763</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>583</v>
+        <v>731</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>170</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>584</v>
+        <v>732</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>616</v>
+        <v>764</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>586</v>
+        <v>734</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>617</v>
+        <v>765</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
-        <v>618</v>
+        <v>766</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>47</v>
@@ -7268,24 +8746,24 @@
         <v>48</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>437</v>
+        <v>585</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>619</v>
+        <v>767</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>620</v>
+        <v>768</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>621</v>
+        <v>769</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
-        <v>622</v>
+        <v>770</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>47</v>
@@ -7294,24 +8772,24 @@
         <v>48</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>437</v>
+        <v>585</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>623</v>
+        <v>771</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>620</v>
+        <v>768</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>624</v>
+        <v>772</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
-        <v>625</v>
+        <v>773</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>47</v>
@@ -7320,24 +8798,24 @@
         <v>48</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>437</v>
+        <v>585</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>626</v>
+        <v>774</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>620</v>
+        <v>768</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>627</v>
+        <v>775</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2" t="s">
-        <v>628</v>
+        <v>776</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>47</v>
@@ -7346,24 +8824,24 @@
         <v>48</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>437</v>
+        <v>585</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>629</v>
+        <v>777</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>620</v>
+        <v>768</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>630</v>
+        <v>778</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2" t="s">
-        <v>631</v>
+        <v>779</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>47</v>
@@ -7372,24 +8850,24 @@
         <v>48</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>437</v>
+        <v>585</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>632</v>
+        <v>780</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>620</v>
+        <v>768</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>633</v>
+        <v>781</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2" t="s">
-        <v>634</v>
+        <v>782</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>47</v>
@@ -7398,284 +8876,284 @@
         <v>48</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>437</v>
+        <v>585</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>635</v>
+        <v>783</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>620</v>
+        <v>768</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>636</v>
+        <v>784</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2" t="s">
-        <v>637</v>
+        <v>785</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>638</v>
+        <v>786</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>73</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>639</v>
+        <v>787</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>640</v>
+        <v>788</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>641</v>
+        <v>789</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>642</v>
+        <v>790</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2" t="s">
-        <v>643</v>
+        <v>791</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>638</v>
+        <v>786</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>73</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>639</v>
+        <v>787</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>644</v>
+        <v>792</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>641</v>
+        <v>789</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>645</v>
+        <v>793</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
-        <v>646</v>
+        <v>794</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>638</v>
+        <v>786</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>73</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>639</v>
+        <v>787</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>647</v>
+        <v>795</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>641</v>
+        <v>789</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>648</v>
+        <v>796</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="s">
-        <v>649</v>
+        <v>797</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>638</v>
+        <v>786</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>73</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>639</v>
+        <v>787</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>650</v>
+        <v>798</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>641</v>
+        <v>789</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>651</v>
+        <v>799</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2" t="s">
-        <v>652</v>
+        <v>800</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>638</v>
+        <v>786</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>73</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>639</v>
+        <v>787</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>650</v>
+        <v>798</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>641</v>
+        <v>789</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>653</v>
+        <v>801</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2" t="s">
-        <v>654</v>
+        <v>802</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>638</v>
+        <v>786</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>73</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>639</v>
+        <v>787</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>650</v>
+        <v>798</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>641</v>
+        <v>789</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>655</v>
+        <v>803</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2" t="s">
-        <v>656</v>
+        <v>804</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>638</v>
+        <v>786</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>73</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>639</v>
+        <v>787</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>650</v>
+        <v>798</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>641</v>
+        <v>789</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>657</v>
+        <v>805</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2" t="s">
-        <v>658</v>
+        <v>806</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>638</v>
+        <v>786</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>73</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>639</v>
+        <v>787</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>650</v>
+        <v>798</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>641</v>
+        <v>789</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>659</v>
+        <v>807</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2" t="s">
-        <v>660</v>
+        <v>808</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>638</v>
+        <v>786</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>73</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>639</v>
+        <v>787</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>661</v>
+        <v>809</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>641</v>
+        <v>789</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>662</v>
+        <v>810</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
-        <v>663</v>
+        <v>811</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>638</v>
+        <v>786</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>73</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>639</v>
+        <v>787</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>664</v>
+        <v>812</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>641</v>
+        <v>789</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>665</v>
+        <v>813</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
-        <v>666</v>
+        <v>814</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>270</v>
@@ -7684,24 +9162,24 @@
         <v>259</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>667</v>
+        <v>815</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>668</v>
+        <v>816</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>669</v>
+        <v>817</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>670</v>
+        <v>818</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
-        <v>671</v>
+        <v>819</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>270</v>
@@ -7710,24 +9188,24 @@
         <v>259</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>667</v>
+        <v>815</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>672</v>
+        <v>820</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>673</v>
+        <v>821</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>674</v>
+        <v>822</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2" t="s">
-        <v>675</v>
+        <v>823</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>177</v>
@@ -7736,24 +9214,24 @@
         <v>170</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>667</v>
+        <v>815</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>676</v>
+        <v>824</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>677</v>
+        <v>825</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>678</v>
+        <v>826</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2" t="s">
-        <v>679</v>
+        <v>827</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>210</v>
@@ -7762,50 +9240,50 @@
         <v>199</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>680</v>
+        <v>828</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>681</v>
+        <v>829</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>682</v>
+        <v>830</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>683</v>
+        <v>831</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2" t="s">
-        <v>684</v>
+        <v>832</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>685</v>
+        <v>833</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>48</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>680</v>
+        <v>828</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>686</v>
+        <v>834</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>687</v>
+        <v>835</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>688</v>
+        <v>836</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
-        <v>689</v>
+        <v>837</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>164</v>
@@ -7814,24 +9292,24 @@
         <v>118</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>680</v>
+        <v>828</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>690</v>
+        <v>838</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>691</v>
+        <v>839</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>692</v>
+        <v>840</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2" t="s">
-        <v>693</v>
+        <v>841</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>315</v>
@@ -7840,24 +9318,24 @@
         <v>118</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>680</v>
+        <v>828</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>694</v>
+        <v>842</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>695</v>
+        <v>843</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>696</v>
+        <v>844</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
-        <v>697</v>
+        <v>845</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>72</v>
@@ -7866,50 +9344,50 @@
         <v>73</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>680</v>
+        <v>828</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>698</v>
+        <v>846</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>699</v>
+        <v>847</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>700</v>
+        <v>848</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2" t="s">
-        <v>701</v>
+        <v>849</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>702</v>
+        <v>850</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>170</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>703</v>
+        <v>851</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>704</v>
+        <v>852</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>705</v>
+        <v>853</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>706</v>
+        <v>854</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2" t="s">
-        <v>707</v>
+        <v>855</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>253</v>
@@ -7918,24 +9396,24 @@
         <v>118</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>703</v>
+        <v>851</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>708</v>
+        <v>856</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>709</v>
+        <v>857</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>710</v>
+        <v>858</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
-        <v>711</v>
+        <v>859</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>281</v>
@@ -7944,24 +9422,24 @@
         <v>282</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>680</v>
+        <v>828</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>712</v>
+        <v>860</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>713</v>
+        <v>861</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>714</v>
+        <v>862</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
-        <v>715</v>
+        <v>863</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>139</v>
@@ -7970,24 +9448,24 @@
         <v>118</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>680</v>
+        <v>828</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>716</v>
+        <v>864</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>717</v>
+        <v>865</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>718</v>
+        <v>866</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2" t="s">
-        <v>719</v>
+        <v>867</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>42</v>
@@ -7996,24 +9474,24 @@
         <v>12</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>720</v>
+        <v>868</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>721</v>
+        <v>869</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>722</v>
+        <v>870</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>723</v>
+        <v>871</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2" t="s">
-        <v>724</v>
+        <v>872</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>305</v>
@@ -8022,19 +9500,19 @@
         <v>282</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>703</v>
+        <v>851</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>725</v>
+        <v>873</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>726</v>
+        <v>874</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>727</v>
+        <v>875</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>728</v>
+        <v>876</v>
       </c>
     </row>
   </sheetData>
@@ -8064,16 +9542,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>729</v>
+        <v>877</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>730</v>
+        <v>878</v>
       </c>
       <c r="B3" s="5" t="n">
         <f aca="false">COUNTA('Story Status'!A:A)-1</f>
-        <v>72</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8096,16 +9574,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>731</v>
+        <v>879</v>
       </c>
       <c r="B6" s="5" t="n">
         <f aca="false">COUNTIF('Story Status'!J:J,"Not Started")</f>
-        <v>14</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>732</v>
+        <v>880</v>
       </c>
       <c r="B7" s="5" t="n">
         <f aca="false">SUMIFS('Story Status'!H:H,'Story Status'!J:J,"Done")</f>
@@ -8114,16 +9592,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>733</v>
+        <v>881</v>
       </c>
       <c r="B8" s="5" t="n">
         <f aca="false">SUM('Story Status'!H:H)</f>
-        <v>244</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>734</v>
+        <v>882</v>
       </c>
       <c r="B9" s="5" t="n">
         <f aca="false">COUNTIFS('Test Cases'!D:D,"&lt;&gt;*Manual*",'Test Cases'!G:G,"Pass")</f>
@@ -8132,7 +9610,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>735</v>
+        <v>883</v>
       </c>
       <c r="B10" s="5" t="n">
         <f aca="false">COUNTIFS('Test Cases'!D:D,"*Manual*",'Test Cases'!G:G,"Pass")+COUNTIFS('Test Cases'!D:D,"System",'Test Cases'!G:G,"Pass")+COUNTIFS('Test Cases'!D:D,"Gate",'Test Cases'!G:G,"Pass")</f>
@@ -8141,7 +9619,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>736</v>
+        <v>884</v>
       </c>
       <c r="B11" s="5" t="n">
         <f aca="false">COUNTIF('Test Cases'!G:G,"Not Run")</f>
